--- a/代码目录.xlsx
+++ b/代码目录.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21540" windowHeight="10170"/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
   <si>
     <t>名称</t>
   </si>
@@ -97,6 +97,12 @@
     <t>牛散持仓情况非母版.py</t>
   </si>
   <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>网站不再更新</t>
+  </si>
+  <si>
     <t>牛散持仓情况母版.py</t>
   </si>
   <si>
@@ -107,9 +113,6 @@
   </si>
   <si>
     <t>千古千评.py</t>
-  </si>
-  <si>
-    <t>N</t>
   </si>
   <si>
     <t>抢药.py</t>
@@ -1082,7 +1085,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="28.5" spans="1:3">
+    <row r="2" ht="14.25" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1093,27 +1096,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="28.5" spans="1:3">
+    <row r="3" ht="14.25" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" ht="28.5" spans="1:3">
+    <row r="4" ht="14.25" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" ht="42.75" spans="1:3">
+    <row r="5" ht="14.25" spans="1:3">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" ht="42.75" spans="1:3">
+    <row r="6" ht="14.25" spans="1:3">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" ht="42.75" spans="1:3">
+    <row r="7" ht="14.25" spans="1:3">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -1124,12 +1127,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" ht="42.75" spans="1:3">
+    <row r="8" ht="14.25" spans="1:3">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" ht="28.5" spans="1:3">
+    <row r="9" ht="14.25" spans="1:3">
       <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
@@ -1140,12 +1143,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" ht="28.5" spans="1:3">
+    <row r="10" ht="14.25" spans="1:3">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" ht="57" spans="1:3">
+    <row r="11" ht="14.25" spans="1:3">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -1156,71 +1159,98 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" ht="28.5" spans="1:3">
+    <row r="12" ht="14.25" spans="1:3">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" ht="28.5" spans="1:3">
+    <row r="13" ht="14.25" spans="1:3">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="14" ht="42.75" spans="1:3">
+    <row r="14" ht="14.25" spans="1:3">
       <c r="A14" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="15" ht="42.75" spans="1:3">
+    <row r="15" ht="14.25" spans="1:3">
       <c r="A15" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="16" ht="42.75" spans="1:3">
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25" spans="1:3">
       <c r="A16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="17" ht="28.5" spans="1:3">
+      <c r="C16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25" spans="1:3">
       <c r="A17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="18" ht="42.75" spans="1:3">
+    <row r="18" ht="14.25" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" ht="28.5" spans="1:3">
+        <v>26</v>
+      </c>
+      <c r="B18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>22</v>
+      </c>
+      <c r="C19" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="20" ht="14.25" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" ht="14.25" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B21" t="s">
         <v>4</v>
       </c>
       <c r="C21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" ht="14.25" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
